--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ35"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2836,27 +2836,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>98306695</v>
+        <v>136864308</v>
       </c>
       <c r="B20" t="n">
-        <v>57950</v>
+        <v>58021</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2873,22 +2873,23 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nacka, Sundsvall, Mpd</t>
+          <t>Stig till småbåtshamnen , Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>623590</v>
+        <v>624121</v>
       </c>
       <c r="R20" t="n">
-        <v>6929264</v>
+        <v>6929327</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2912,22 +2913,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-01-25</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-01-25</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2942,24 +2943,24 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Rode Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Rode Nordin, Ulla Hellman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98306695</t>
+          <t>https://artportalen.se/Sighting/136864308</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>98838317</v>
+        <v>98306695</v>
       </c>
       <c r="B21" t="n">
         <v>57950</v>
@@ -2989,26 +2990,26 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Nacka 107, Sundsvall, Mpd</t>
+          <t>Nacka, Sundsvall, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>623927</v>
+        <v>623590</v>
       </c>
       <c r="R21" t="n">
-        <v>6929206</v>
+        <v>6929264</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3035,22 +3036,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2022-01-25</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2022-01-25</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3076,13 +3077,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98838317</t>
+          <t>https://artportalen.se/Sighting/98306695</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131542047</v>
+        <v>98838317</v>
       </c>
       <c r="B22" t="n">
         <v>57950</v>
@@ -3112,30 +3113,29 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nacka, Alnö, Mpd</t>
+          <t>Nacka 107, Sundsvall, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>624293</v>
+        <v>623927</v>
       </c>
       <c r="R22" t="n">
-        <v>6929183</v>
+        <v>6929206</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3159,27 +3159,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Trumning</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3194,27 +3189,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Thomas Engström</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Thomas Engström</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131542047</t>
+          <t>https://artportalen.se/Sighting/98838317</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128317477</v>
+        <v>131542047</v>
       </c>
       <c r="B23" t="n">
-        <v>57258</v>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3222,16 +3217,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100065</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3241,24 +3236,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>sträckande S</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Nacka, Alnö, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>623908</v>
+        <v>624293</v>
       </c>
       <c r="R23" t="n">
-        <v>6929204</v>
+        <v>6929183</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3285,22 +3283,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Trumning</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3326,33 +3329,33 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128317477</t>
+          <t>https://artportalen.se/Sighting/131542047</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132451882</v>
+        <v>128317477</v>
       </c>
       <c r="B24" t="n">
-        <v>57975</v>
+        <v>57258</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>100065</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3362,31 +3365,24 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>sträckande S</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Småbåtshamnen, Nacka, Mpd</t>
+          <t>Nacka, Alnö, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>623993</v>
+        <v>623908</v>
       </c>
       <c r="R24" t="n">
-        <v>6929482</v>
+        <v>6929204</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3413,22 +3409,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3454,38 +3450,38 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132451882</t>
+          <t>https://artportalen.se/Sighting/128317477</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129724736</v>
+        <v>132451882</v>
       </c>
       <c r="B25" t="n">
-        <v>57945</v>
+        <v>57975</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3507,14 +3503,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>nacka, Mpd</t>
+          <t>Småbåtshamnen, Nacka, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>624322</v>
+        <v>623993</v>
       </c>
       <c r="R25" t="n">
-        <v>6929299</v>
+        <v>6929482</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3541,7 +3537,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -3551,12 +3547,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3571,71 +3567,78 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Piero Crotto</t>
+          <t>Thomas Engström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Piero Crotto</t>
+          <t>Thomas Engström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129724736</t>
+          <t>https://artportalen.se/Sighting/132451882</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130943171</v>
+        <v>129724736</v>
       </c>
       <c r="B26" t="n">
-        <v>56338</v>
+        <v>57945</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100127</v>
+        <v>100110</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Öring</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Salmo trutta</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>eDNA</t>
-        </is>
-      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>bäck N Alnön, Gista, Mpd</t>
+          <t>nacka, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>623601</v>
+        <v>624322</v>
       </c>
       <c r="R26" t="n">
-        <v>6929218</v>
+        <v>6929299</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3662,12 +3665,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3676,38 +3689,33 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Oskar Norrgrann</t>
+          <t>Piero Crotto</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Oskar Norrgrann</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Fiskinventering med eDNA</t>
-        </is>
-      </c>
+          <t>Piero Crotto</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130943171</t>
+          <t>https://artportalen.se/Sighting/129724736</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117625484</v>
+        <v>130943171</v>
       </c>
       <c r="B27" t="n">
-        <v>58195</v>
+        <v>56338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3715,49 +3723,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102122</v>
+        <v>100127</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Flodsångare</t>
+          <t>Öring</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Locustella fluviatilis</t>
+          <t>Salmo trutta</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Wolf, 1810)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>eDNA</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nacka, Alnö, Mpd</t>
+          <t>bäck N Alnön, Gista, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>624191</v>
+        <v>623601</v>
       </c>
       <c r="R27" t="n">
-        <v>6929390</v>
+        <v>6929218</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3781,22 +3786,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3805,75 +3800,85 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Thomas Engström</t>
+          <t>Oskar Norrgrann</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Thomas Engström</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Oskar Norrgrann</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Fiskinventering med eDNA</t>
+        </is>
+      </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117625484</t>
+          <t>https://artportalen.se/Sighting/130943171</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>97321744</v>
+        <v>117625484</v>
       </c>
       <c r="B28" t="n">
-        <v>58592</v>
+        <v>58195</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102125</v>
+        <v>102122</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Flodsångare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Locustella fluviatilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wolf, 1810)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Eriksdal 138, Sundsvall, Mpd</t>
+          <t>Nacka, Alnö, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>623378</v>
+        <v>624191</v>
       </c>
       <c r="R28" t="n">
-        <v>6929264</v>
+        <v>6929390</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3900,22 +3905,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2021-11-27</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2021-11-27</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3930,44 +3935,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Thomas Engström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Thomas Engström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97321744</t>
+          <t>https://artportalen.se/Sighting/117625484</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128767522</v>
+        <v>97321744</v>
       </c>
       <c r="B29" t="n">
-        <v>57794</v>
+        <v>58592</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102621</v>
+        <v>102125</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3977,30 +3982,25 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nacka, Alnö, Mpd</t>
+          <t>Eriksdal 138, Sundsvall, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>624293</v>
+        <v>623378</v>
       </c>
       <c r="R29" t="n">
-        <v>6929183</v>
+        <v>6929264</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4024,22 +4024,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2021-11-27</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2021-11-27</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4054,27 +4054,27 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Thomas Engström</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Thomas Engström</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128767522</t>
+          <t>https://artportalen.se/Sighting/97321744</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127058811</v>
+        <v>128767522</v>
       </c>
       <c r="B30" t="n">
-        <v>57369</v>
+        <v>57794</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4082,49 +4082,49 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102961</v>
+        <v>102621</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Småbåtshamnen, Nacka, Mpd</t>
+          <t>Nacka, Alnö, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>624034</v>
+        <v>624293</v>
       </c>
       <c r="R30" t="n">
-        <v>6929466</v>
+        <v>6929183</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4148,22 +4148,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4189,33 +4189,33 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127058811</t>
+          <t>https://artportalen.se/Sighting/128767522</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>103586832</v>
+        <v>127058811</v>
       </c>
       <c r="B31" t="n">
-        <v>57569</v>
+        <v>57369</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102967</v>
+        <v>102961</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Havstrut</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Larus marinus</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4230,18 +4230,22 @@
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Nackadalbäckens utlopp , Nacka, Alnö, Mpd</t>
+          <t>Småbåtshamnen, Nacka, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>623622</v>
+        <v>624034</v>
       </c>
       <c r="R31" t="n">
-        <v>6929266</v>
+        <v>6929466</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4268,22 +4272,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4298,74 +4302,70 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Rode Nordin</t>
+          <t>Thomas Engström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Rode Nordin, Eva Norén</t>
+          <t>Thomas Engström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103586832</t>
+          <t>https://artportalen.se/Sighting/127058811</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>94188964</v>
+        <v>103586832</v>
       </c>
       <c r="B32" t="n">
-        <v>58420</v>
+        <v>57569</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102992</v>
+        <v>102967</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Näktergal</t>
+          <t>Havstrut</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Luscinia luscinia</t>
+          <t>Larus marinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gistabäcken, Alnö, Mpd</t>
+          <t>Nackadalbäckens utlopp , Nacka, Alnö, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>623585</v>
+        <v>623622</v>
       </c>
       <c r="R32" t="n">
-        <v>6929245</v>
+        <v>6929266</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4392,22 +4392,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2021-06-11</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2021-06-11</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4422,69 +4422,77 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Thomas Engström</t>
+          <t>Rode Nordin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Thomas Engström</t>
+          <t>Rode Nordin, Eva Norén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94188964</t>
+          <t>https://artportalen.se/Sighting/103586832</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132892673</v>
+        <v>94188964</v>
       </c>
       <c r="B33" t="n">
-        <v>101974</v>
+        <v>58420</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220075</v>
+        <v>102992</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Näktergal</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chrysosplenium alternifolium</t>
+          <t>Luscinia luscinia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nacka, Alnö, Mpd</t>
+          <t>Gistabäcken, Alnö, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>624293</v>
+        <v>623585</v>
       </c>
       <c r="R33" t="n">
-        <v>6929183</v>
+        <v>6929245</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4508,12 +4516,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2021-06-11</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2021-06-11</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4522,7 +4540,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4540,47 +4557,44 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892673</t>
+          <t>https://artportalen.se/Sighting/94188964</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132892657</v>
+        <v>132892673</v>
       </c>
       <c r="B34" t="n">
-        <v>84199</v>
+        <v>101974</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>232272</v>
+        <v>220075</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Scharlakansskål</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcoscypha austriaca</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Beck) Boud.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4588,13 +4602,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>624269</v>
+        <v>624293</v>
       </c>
       <c r="R34" t="n">
-        <v>6929358</v>
+        <v>6929183</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4650,16 +4664,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132892657</t>
+          <t>https://artportalen.se/Sighting/132892673</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130943137</v>
+        <v>132892657</v>
       </c>
       <c r="B35" t="n">
-        <v>56312</v>
+        <v>84199</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4667,46 +4681,44 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>234372</v>
+        <v>232272</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sik</t>
+          <t>Scharlakansskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Coregonus maraena</t>
+          <t>Sarcoscypha austriaca</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Bloch, 1779)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Beck) Boud.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>eDNA</t>
-        </is>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>bäck N Alnön, Gista, Mpd</t>
+          <t>Nacka, Alnö, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>623601</v>
+        <v>624269</v>
       </c>
       <c r="R35" t="n">
-        <v>6929218</v>
+        <v>6929358</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4730,12 +4742,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4751,20 +4763,132 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
+          <t>Thomas Engström</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Thomas Engström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132892657</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>130943137</v>
+      </c>
+      <c r="B36" t="n">
+        <v>56312</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>234372</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Sik</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Coregonus maraena</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Bloch, 1779)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>eDNA</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>bäck N Alnön, Gista, Mpd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>623601</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6929218</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
           <t>Oskar Norrgrann</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
+      <c r="AX36" t="inlineStr">
         <is>
           <t>Oskar Norrgrann</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr">
+      <c r="AY36" t="inlineStr">
         <is>
           <t>Fiskinventering med eDNA</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
+      <c r="AZ36" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/130943137</t>
         </is>
@@ -4806,6 +4930,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -2879,7 +2879,7 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stig till småbåtshamnen , Mpd</t>
+          <t>Stig till småbåtshamnen , Nacka, Alnö, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -2591,7 +2591,7 @@
         <v>123291378</v>
       </c>
       <c r="B18" t="n">
-        <v>57966</v>
+        <v>58021</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>131642580</v>
       </c>
       <c r="B19" t="n">
-        <v>57988</v>
+        <v>58021</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>129724736</v>
       </c>
       <c r="B26" t="n">
-        <v>57945</v>
+        <v>58000</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>97321744</v>
       </c>
       <c r="B29" t="n">
-        <v>58592</v>
+        <v>58647</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -2591,7 +2591,7 @@
         <v>123291378</v>
       </c>
       <c r="B18" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>131642580</v>
       </c>
       <c r="B19" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>136864308</v>
       </c>
       <c r="B20" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>129724736</v>
       </c>
       <c r="B26" t="n">
-        <v>58000</v>
+        <v>58013</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>97321744</v>
       </c>
       <c r="B29" t="n">
-        <v>58647</v>
+        <v>58660</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -2591,7 +2591,7 @@
         <v>123291378</v>
       </c>
       <c r="B18" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>131642580</v>
       </c>
       <c r="B19" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>136864308</v>
       </c>
       <c r="B20" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>129724736</v>
       </c>
       <c r="B26" t="n">
-        <v>58013</v>
+        <v>58015</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>97321744</v>
       </c>
       <c r="B29" t="n">
-        <v>58660</v>
+        <v>58662</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -2623,11 +2623,7 @@
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2747,11 +2743,7 @@
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2871,11 +2863,7 @@
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3618,16 +3606,8 @@
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -2591,7 +2591,7 @@
         <v>123291378</v>
       </c>
       <c r="B18" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>131642580</v>
       </c>
       <c r="B19" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>136864308</v>
       </c>
       <c r="B20" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>129724736</v>
       </c>
       <c r="B26" t="n">
-        <v>58015</v>
+        <v>58025</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>97321744</v>
       </c>
       <c r="B29" t="n">
-        <v>58662</v>
+        <v>58672</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -2591,7 +2591,7 @@
         <v>123291378</v>
       </c>
       <c r="B18" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>131642580</v>
       </c>
       <c r="B19" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>136864308</v>
       </c>
       <c r="B20" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>129724736</v>
       </c>
       <c r="B26" t="n">
-        <v>58025</v>
+        <v>58026</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>97321744</v>
       </c>
       <c r="B29" t="n">
-        <v>58672</v>
+        <v>58674</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -2591,7 +2591,7 @@
         <v>123291378</v>
       </c>
       <c r="B18" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>131642580</v>
       </c>
       <c r="B19" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>136864308</v>
       </c>
       <c r="B20" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>129724736</v>
       </c>
       <c r="B26" t="n">
-        <v>58026</v>
+        <v>58027</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>97321744</v>
       </c>
       <c r="B29" t="n">
-        <v>58674</v>
+        <v>58676</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -2591,7 +2591,7 @@
         <v>123291378</v>
       </c>
       <c r="B18" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>131642580</v>
       </c>
       <c r="B19" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>136864308</v>
       </c>
       <c r="B20" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>129724736</v>
       </c>
       <c r="B26" t="n">
-        <v>58027</v>
+        <v>58030</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>97321744</v>
       </c>
       <c r="B29" t="n">
-        <v>58676</v>
+        <v>58679</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
